--- a/tests/fixtures/openlists/hse_program_list.xlsx
+++ b/tests/fixtures/openlists/hse_program_list.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Маркетинг" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Платные места" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="36634049850_Budget" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,41 +413,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Национальный исследовательский университет «Высшая школа экономики»</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Списки зарегистрированных абитуриентов магистратуры. Москва</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>38.04.02 Менеджмент. Образовательная программа «Маркетинг и рыночная аналитика»</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Очная форма обучения, бюджетные места. Количество мест: 25</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Список сформирован по состоянию на 14.08.2026 12:00</t>
+          <t>Список лиц, подавших документы Образовательная программа "Анализ данных в биологии и медицине" Направление подготовки 01.04.02 Прикладная математика и информатика Москва</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Время формирования: 12.08.2026 15:39:18</t>
         </is>
       </c>
     </row>
@@ -460,228 +438,457 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Индивидуальный номер</t>
+          <t>Рег. номер</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Уникальный код поступающего</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Поступление на места по целевой квоте</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Приоритет бюджетного места</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Приоритет целевого места</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Конкурс портфолио</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>Сумма конкурсных баллов</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Вступительное испытание</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Индивидуальные достижения</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Приоритет</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Сумма конкурсных баллов в рамках квоты на целевые места</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Все оценки положительные</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Статус участия в конкурсе</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>Согласие на зачисление</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Статус</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Возврат документов</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Вид документа об образовании</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Предложение размещено на платформе "Работа в России"</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Номер предложения на платформе "Работа в России"</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Идентификационный номер заказчика (предложение не размещено на платформе "Работа в России")</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1000004</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>98</v>
-      </c>
-      <c r="D8" t="n">
-        <v>93</v>
-      </c>
-      <c r="E8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Участвует в конкурсе</t>
+          <t>~36904581266~</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1000117</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>91</v>
-      </c>
-      <c r="D9" t="n">
-        <v>91</v>
+          <t>26496</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>9000001</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>100</v>
+      </c>
+      <c r="I9" t="n">
+        <v>100</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Участвует в конкурсе</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Диплом бакалавра</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>Нет</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Участвует в конкурсе</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1000238</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>76</v>
-      </c>
-      <c r="D10" t="n">
-        <v>66</v>
+          <t>25669</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>9000002</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Участвует в конкурсе</t>
+        <v>2</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Ожидание результатов ВИ</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Диплом бакалавра</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Нет</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>17669</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>9000003</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Ожидание результатов ВИ</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Диплом бакалавра с отличием</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
         <v>4</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1000411</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>22968</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>9000004</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>На рассмотрении</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Диплом бакалавра</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>16711</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>9000005</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>41</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Ожидание результатов ВИ</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Диплом специалиста</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>21639</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>9000006</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
         <v>3</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Ожидание результатов ВИ</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Диплом бакалавра</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Не явился</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Образовательная программа «Маркетинг и рыночная аналитика», платные места</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>№</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Индивидуальный номер</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Сумма конкурсных баллов</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Приоритет</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Согласие</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2000001</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>60</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Да</t>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Зачет результатов олимпиад:</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Олимпиада студентов и выпускников «Высшая лига»</t>
         </is>
       </c>
     </row>
